--- a/artfynd/A 52943-2020 artfynd.xlsx
+++ b/artfynd/A 52943-2020 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123257515</v>
+        <v>123257448</v>
       </c>
       <c r="B2" t="n">
-        <v>57848</v>
+        <v>90917</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,31 +691,26 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103015</v>
+        <v>5447</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -723,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>519210</v>
+        <v>519256</v>
       </c>
       <c r="R2" t="n">
-        <v>6704061</v>
+        <v>6704021</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -767,6 +762,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -785,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123257448</v>
+        <v>123257273</v>
       </c>
       <c r="B3" t="n">
-        <v>90917</v>
+        <v>90952</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,25 +793,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -828,10 +824,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>519256</v>
+        <v>519193</v>
       </c>
       <c r="R3" t="n">
-        <v>6704021</v>
+        <v>6704068</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -891,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123257273</v>
+        <v>123257477</v>
       </c>
       <c r="B4" t="n">
-        <v>90952</v>
+        <v>57494</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -907,26 +903,31 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -934,10 +935,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>519193</v>
+        <v>519247</v>
       </c>
       <c r="R4" t="n">
-        <v>6704068</v>
+        <v>6704021</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -972,13 +973,17 @@
           <t>2025-03-16</t>
         </is>
       </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Hack nedtill på äldre gran</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -997,10 +1002,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123257477</v>
+        <v>123257515</v>
       </c>
       <c r="B5" t="n">
-        <v>57494</v>
+        <v>57848</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1009,20 +1014,20 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1035,7 +1040,7 @@
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -1045,10 +1050,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>519247</v>
+        <v>519210</v>
       </c>
       <c r="R5" t="n">
-        <v>6704021</v>
+        <v>6704061</v>
       </c>
       <c r="S5" t="n">
         <v>50</v>
@@ -1081,11 +1086,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-03-16</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Hack nedtill på äldre gran</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 52943-2020 artfynd.xlsx
+++ b/artfynd/A 52943-2020 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123257448</v>
+        <v>123257273</v>
       </c>
       <c r="B2" t="n">
-        <v>90917</v>
+        <v>90952</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -718,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>519256</v>
+        <v>519193</v>
       </c>
       <c r="R2" t="n">
-        <v>6704021</v>
+        <v>6704068</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123257273</v>
+        <v>123257448</v>
       </c>
       <c r="B3" t="n">
-        <v>90952</v>
+        <v>90917</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,25 +793,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -824,10 +824,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>519193</v>
+        <v>519256</v>
       </c>
       <c r="R3" t="n">
-        <v>6704068</v>
+        <v>6704021</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>

--- a/artfynd/A 52943-2020 artfynd.xlsx
+++ b/artfynd/A 52943-2020 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123257273</v>
       </c>
       <c r="B2" t="n">
-        <v>90952</v>
+        <v>90955</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123257448</v>
+        <v>123257477</v>
       </c>
       <c r="B3" t="n">
-        <v>90917</v>
+        <v>57497</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,30 +793,35 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -824,7 +829,7 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>519256</v>
+        <v>519247</v>
       </c>
       <c r="R3" t="n">
         <v>6704021</v>
@@ -862,13 +867,17 @@
           <t>2025-03-16</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Hack nedtill på äldre gran</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -887,10 +896,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123257477</v>
+        <v>123257448</v>
       </c>
       <c r="B4" t="n">
-        <v>57494</v>
+        <v>90920</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -899,35 +908,30 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -935,7 +939,7 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>519247</v>
+        <v>519256</v>
       </c>
       <c r="R4" t="n">
         <v>6704021</v>
@@ -973,17 +977,13 @@
           <t>2025-03-16</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Hack nedtill på äldre gran</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1005,7 +1005,7 @@
         <v>123257515</v>
       </c>
       <c r="B5" t="n">
-        <v>57848</v>
+        <v>57851</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 52943-2020 artfynd.xlsx
+++ b/artfynd/A 52943-2020 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123257273</v>
+        <v>123257477</v>
       </c>
       <c r="B2" t="n">
-        <v>90955</v>
+        <v>57497</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,26 +691,31 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -718,10 +723,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>519193</v>
+        <v>519247</v>
       </c>
       <c r="R2" t="n">
-        <v>6704068</v>
+        <v>6704021</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -756,13 +761,17 @@
           <t>2025-03-16</t>
         </is>
       </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Hack nedtill på äldre gran</t>
+        </is>
+      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -781,10 +790,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123257477</v>
+        <v>123257448</v>
       </c>
       <c r="B3" t="n">
-        <v>57497</v>
+        <v>90922</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,35 +802,30 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -829,7 +833,7 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>519247</v>
+        <v>519256</v>
       </c>
       <c r="R3" t="n">
         <v>6704021</v>
@@ -867,17 +871,13 @@
           <t>2025-03-16</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Hack nedtill på äldre gran</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -896,10 +896,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123257448</v>
+        <v>123257515</v>
       </c>
       <c r="B4" t="n">
-        <v>90920</v>
+        <v>57851</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -912,26 +912,31 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5447</v>
+        <v>103015</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -939,10 +944,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>519256</v>
+        <v>519210</v>
       </c>
       <c r="R4" t="n">
-        <v>6704021</v>
+        <v>6704061</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -983,7 +988,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1002,10 +1006,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123257515</v>
+        <v>123257273</v>
       </c>
       <c r="B5" t="n">
-        <v>57851</v>
+        <v>90957</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1014,35 +1018,30 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103015</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1050,10 +1049,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>519210</v>
+        <v>519193</v>
       </c>
       <c r="R5" t="n">
-        <v>6704061</v>
+        <v>6704068</v>
       </c>
       <c r="S5" t="n">
         <v>50</v>
@@ -1094,6 +1093,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 52943-2020 artfynd.xlsx
+++ b/artfynd/A 52943-2020 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123257477</v>
+        <v>123257273</v>
       </c>
       <c r="B2" t="n">
-        <v>57497</v>
+        <v>90963</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,31 +691,26 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -723,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>519247</v>
+        <v>519193</v>
       </c>
       <c r="R2" t="n">
-        <v>6704021</v>
+        <v>6704068</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -761,17 +756,13 @@
           <t>2025-03-16</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Hack nedtill på äldre gran</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -793,7 +784,7 @@
         <v>123257448</v>
       </c>
       <c r="B3" t="n">
-        <v>90922</v>
+        <v>90928</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -1006,10 +997,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123257273</v>
+        <v>123257477</v>
       </c>
       <c r="B5" t="n">
-        <v>90957</v>
+        <v>57497</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1022,26 +1013,31 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1049,10 +1045,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>519193</v>
+        <v>519247</v>
       </c>
       <c r="R5" t="n">
-        <v>6704068</v>
+        <v>6704021</v>
       </c>
       <c r="S5" t="n">
         <v>50</v>
@@ -1087,13 +1083,17 @@
           <t>2025-03-16</t>
         </is>
       </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Hack nedtill på äldre gran</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 52943-2020 artfynd.xlsx
+++ b/artfynd/A 52943-2020 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123257448</v>
+        <v>123257515</v>
       </c>
       <c r="B2" t="n">
-        <v>90931</v>
+        <v>57857</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,26 +691,31 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5447</v>
+        <v>103015</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -718,10 +723,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>519256</v>
+        <v>519210</v>
       </c>
       <c r="R2" t="n">
-        <v>6704021</v>
+        <v>6704061</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -762,7 +767,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -781,10 +785,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123257477</v>
+        <v>123257273</v>
       </c>
       <c r="B3" t="n">
-        <v>57497</v>
+        <v>90983</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,31 +801,26 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -829,10 +828,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>519247</v>
+        <v>519193</v>
       </c>
       <c r="R3" t="n">
-        <v>6704021</v>
+        <v>6704068</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -867,17 +866,13 @@
           <t>2025-03-16</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Hack nedtill på äldre gran</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -896,10 +891,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123257515</v>
+        <v>123257448</v>
       </c>
       <c r="B4" t="n">
-        <v>57851</v>
+        <v>90948</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -912,31 +907,26 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103015</v>
+        <v>5447</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -944,10 +934,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>519210</v>
+        <v>519256</v>
       </c>
       <c r="R4" t="n">
-        <v>6704061</v>
+        <v>6704021</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -988,6 +978,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1006,10 +997,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123257273</v>
+        <v>123257477</v>
       </c>
       <c r="B5" t="n">
-        <v>90966</v>
+        <v>57503</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1022,26 +1013,31 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1049,10 +1045,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>519193</v>
+        <v>519247</v>
       </c>
       <c r="R5" t="n">
-        <v>6704068</v>
+        <v>6704021</v>
       </c>
       <c r="S5" t="n">
         <v>50</v>
@@ -1087,13 +1083,17 @@
           <t>2025-03-16</t>
         </is>
       </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Hack nedtill på äldre gran</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 52943-2020 artfynd.xlsx
+++ b/artfynd/A 52943-2020 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123257515</v>
       </c>
       <c r="B2" t="n">
-        <v>57857</v>
+        <v>57860</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -785,10 +785,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123257273</v>
+        <v>123257448</v>
       </c>
       <c r="B3" t="n">
-        <v>90983</v>
+        <v>90953</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,25 +797,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -828,10 +828,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>519193</v>
+        <v>519256</v>
       </c>
       <c r="R3" t="n">
-        <v>6704068</v>
+        <v>6704021</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -891,10 +891,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123257448</v>
+        <v>123257273</v>
       </c>
       <c r="B4" t="n">
-        <v>90948</v>
+        <v>90988</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -903,25 +903,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -934,10 +934,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>519256</v>
+        <v>519193</v>
       </c>
       <c r="R4" t="n">
-        <v>6704021</v>
+        <v>6704068</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -1000,7 +1000,7 @@
         <v>123257477</v>
       </c>
       <c r="B5" t="n">
-        <v>57503</v>
+        <v>57506</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 52943-2020 artfynd.xlsx
+++ b/artfynd/A 52943-2020 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123257515</v>
+        <v>123257273</v>
       </c>
       <c r="B2" t="n">
-        <v>57860</v>
+        <v>90990</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,35 +687,30 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103015</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -723,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>519210</v>
+        <v>519193</v>
       </c>
       <c r="R2" t="n">
-        <v>6704061</v>
+        <v>6704068</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -767,6 +762,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -788,7 +784,7 @@
         <v>123257448</v>
       </c>
       <c r="B3" t="n">
-        <v>90953</v>
+        <v>90955</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -891,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123257273</v>
+        <v>123257477</v>
       </c>
       <c r="B4" t="n">
-        <v>90988</v>
+        <v>57507</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -907,26 +903,31 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -934,10 +935,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>519193</v>
+        <v>519247</v>
       </c>
       <c r="R4" t="n">
-        <v>6704068</v>
+        <v>6704021</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -972,13 +973,17 @@
           <t>2025-03-16</t>
         </is>
       </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Hack nedtill på äldre gran</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -997,10 +1002,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123257477</v>
+        <v>123257515</v>
       </c>
       <c r="B5" t="n">
-        <v>57506</v>
+        <v>57861</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1009,20 +1014,20 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1035,7 +1040,7 @@
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -1045,10 +1050,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>519247</v>
+        <v>519210</v>
       </c>
       <c r="R5" t="n">
-        <v>6704021</v>
+        <v>6704061</v>
       </c>
       <c r="S5" t="n">
         <v>50</v>
@@ -1081,11 +1086,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-03-16</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Hack nedtill på äldre gran</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 52943-2020 artfynd.xlsx
+++ b/artfynd/A 52943-2020 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123257273</v>
+        <v>123257477</v>
       </c>
       <c r="B2" t="n">
-        <v>90990</v>
+        <v>57507</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,26 +691,31 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -718,10 +723,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>519193</v>
+        <v>519247</v>
       </c>
       <c r="R2" t="n">
-        <v>6704068</v>
+        <v>6704021</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -756,13 +761,17 @@
           <t>2025-03-16</t>
         </is>
       </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Hack nedtill på äldre gran</t>
+        </is>
+      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -887,10 +896,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123257477</v>
+        <v>123257515</v>
       </c>
       <c r="B4" t="n">
-        <v>57507</v>
+        <v>57861</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -899,20 +908,20 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -925,7 +934,7 @@
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -935,10 +944,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>519247</v>
+        <v>519210</v>
       </c>
       <c r="R4" t="n">
-        <v>6704021</v>
+        <v>6704061</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -971,11 +980,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-03-16</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Hack nedtill på äldre gran</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1002,10 +1006,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123257515</v>
+        <v>123257273</v>
       </c>
       <c r="B5" t="n">
-        <v>57861</v>
+        <v>90990</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1014,35 +1018,30 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103015</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1050,10 +1049,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>519210</v>
+        <v>519193</v>
       </c>
       <c r="R5" t="n">
-        <v>6704061</v>
+        <v>6704068</v>
       </c>
       <c r="S5" t="n">
         <v>50</v>
@@ -1094,6 +1093,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 52943-2020 artfynd.xlsx
+++ b/artfynd/A 52943-2020 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123257477</v>
+        <v>123257273</v>
       </c>
       <c r="B2" t="n">
-        <v>57507</v>
+        <v>90990</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,31 +691,26 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -723,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>519247</v>
+        <v>519193</v>
       </c>
       <c r="R2" t="n">
-        <v>6704021</v>
+        <v>6704068</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -761,17 +756,13 @@
           <t>2025-03-16</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Hack nedtill på äldre gran</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -790,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123257448</v>
+        <v>123257515</v>
       </c>
       <c r="B3" t="n">
-        <v>90955</v>
+        <v>57861</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -806,26 +797,31 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5447</v>
+        <v>103015</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -833,10 +829,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>519256</v>
+        <v>519210</v>
       </c>
       <c r="R3" t="n">
-        <v>6704021</v>
+        <v>6704061</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -877,7 +873,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -896,10 +891,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123257515</v>
+        <v>123257477</v>
       </c>
       <c r="B4" t="n">
-        <v>57861</v>
+        <v>57507</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -908,20 +903,20 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -934,7 +929,7 @@
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -944,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>519210</v>
+        <v>519247</v>
       </c>
       <c r="R4" t="n">
-        <v>6704061</v>
+        <v>6704021</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -980,6 +975,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-03-16</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Hack nedtill på äldre gran</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1006,10 +1006,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123257273</v>
+        <v>123257448</v>
       </c>
       <c r="B5" t="n">
-        <v>90990</v>
+        <v>90955</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1018,25 +1018,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1049,10 +1049,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>519193</v>
+        <v>519256</v>
       </c>
       <c r="R5" t="n">
-        <v>6704068</v>
+        <v>6704021</v>
       </c>
       <c r="S5" t="n">
         <v>50</v>
